--- a/results/PV_MASTER_RESULTS_CURRENT_PD.xlsx
+++ b/results/PV_MASTER_RESULTS_CURRENT_PD.xlsx
@@ -102,7 +102,7 @@
     <t>QA: Shading hourly diagnostic rows</t>
   </si>
   <si>
-    <t>2026-09-28 13:07:53</t>
+    <t>2026-09-29 13:34:42</t>
   </si>
   <si>
     <t>CURRENT Perez–Driesse master results candidate</t>
@@ -13307,7 +13307,7 @@
         <v>69</v>
       </c>
       <c r="H568" s="4">
-        <v>28.584139</v>
+        <v>29.43188</v>
       </c>
     </row>
     <row r="569" spans="1:8">
@@ -13427,7 +13427,7 @@
         <v>69</v>
       </c>
       <c r="H574" s="4">
-        <v>12.67684</v>
+        <v>13.50964</v>
       </c>
     </row>
     <row r="575" spans="1:8">
@@ -13547,7 +13547,7 @@
         <v>69</v>
       </c>
       <c r="H580" s="4">
-        <v>1220.718566</v>
+        <v>1253.521788</v>
       </c>
     </row>
     <row r="581" spans="1:8">
@@ -13667,7 +13667,7 @@
         <v>70</v>
       </c>
       <c r="H586" s="4">
-        <v>-2.330860999999995</v>
+        <v>-1.48312</v>
       </c>
     </row>
     <row r="587" spans="1:8">
@@ -13787,7 +13787,7 @@
         <v>70</v>
       </c>
       <c r="H592" s="4">
-        <v>-1.190160000000001</v>
+        <v>-0.3573600000000017</v>
       </c>
     </row>
     <row r="593" spans="1:8">
@@ -13907,7 +13907,7 @@
         <v>70</v>
       </c>
       <c r="H598" s="4">
-        <v>-98.63343400000008</v>
+        <v>-65.83021199999985</v>
       </c>
     </row>
     <row r="599" spans="1:8">
@@ -14027,7 +14027,7 @@
         <v>71</v>
       </c>
       <c r="H604" s="4">
-        <v>-0.0753957949215589</v>
+        <v>-0.0479741225942099</v>
       </c>
     </row>
     <row r="605" spans="1:8">
@@ -14147,7 +14147,7 @@
         <v>71</v>
       </c>
       <c r="H610" s="4">
-        <v>-0.0858267830100238</v>
+        <v>-0.0257705343621548</v>
       </c>
     </row>
     <row r="611" spans="1:8">
@@ -14267,7 +14267,7 @@
         <v>71</v>
       </c>
       <c r="H616" s="4">
-        <v>-0.07475899835676909</v>
+        <v>-0.0498958670620121</v>
       </c>
     </row>
     <row r="617" spans="1:8">
@@ -14387,7 +14387,7 @@
         <v>72</v>
       </c>
       <c r="H622" s="4">
-        <v>-7.539579492155895</v>
+        <v>-4.797412259420992</v>
       </c>
     </row>
     <row r="623" spans="1:8">
@@ -14507,7 +14507,7 @@
         <v>72</v>
       </c>
       <c r="H628" s="4">
-        <v>-8.582678301002383</v>
+        <v>-2.577053436215488</v>
       </c>
     </row>
     <row r="629" spans="1:8">
@@ -14627,7 +14627,7 @@
         <v>72</v>
       </c>
       <c r="H634" s="4">
-        <v>-7.475899835676914</v>
+        <v>-4.989586706201214</v>
       </c>
     </row>
     <row r="635" spans="1:8">
@@ -14867,7 +14867,7 @@
         <v>40</v>
       </c>
       <c r="H646" s="4">
-        <v>566.9802434772816</v>
+        <v>213.323633583905</v>
       </c>
     </row>
     <row r="647" spans="1:8">
@@ -14987,7 +14987,7 @@
         <v>41</v>
       </c>
       <c r="H652" s="4">
-        <v>421.6252505643341</v>
+        <v>132.8301467268623</v>
       </c>
     </row>
     <row r="653" spans="1:8">
@@ -15107,7 +15107,7 @@
         <v>42</v>
       </c>
       <c r="H658" s="4">
-        <v>38.07832507510927</v>
+        <v>14.32678961791182</v>
       </c>
     </row>
     <row r="659" spans="1:8">
@@ -15227,7 +15227,7 @@
         <v>43</v>
       </c>
       <c r="H664" s="4">
-        <v>28.31630120372336</v>
+        <v>8.920856705375826</v>
       </c>
     </row>
     <row r="665" spans="1:8">
@@ -15347,7 +15347,7 @@
         <v>44</v>
       </c>
       <c r="H670" s="4">
-        <v>-111.198006772009</v>
+        <v>-74.17405417607223</v>
       </c>
     </row>
     <row r="671" spans="1:8">
@@ -15467,7 +15467,7 @@
         <v>45</v>
       </c>
       <c r="H676" s="4">
-        <v>-7.468044783360117</v>
+        <v>-4.981520572450806</v>
       </c>
     </row>
     <row r="677" spans="1:8">
@@ -15587,7 +15587,7 @@
         <v>46</v>
       </c>
       <c r="H682" s="4">
-        <v>-7.468044783360117</v>
+        <v>-4.981520572450806</v>
       </c>
     </row>
     <row r="683" spans="1:8">
@@ -15707,7 +15707,7 @@
         <v>47</v>
       </c>
       <c r="H688" s="4">
-        <v>0.8437044474005821</v>
+        <v>0.9778747231770684</v>
       </c>
     </row>
     <row r="689" spans="1:8">
@@ -18412,16 +18412,16 @@
         <v>30.915</v>
       </c>
       <c r="F4" s="4">
-        <v>28.584139</v>
+        <v>29.43188</v>
       </c>
       <c r="G4" s="4">
-        <v>-2.330860999999995</v>
+        <v>-1.48312</v>
       </c>
       <c r="H4" s="4">
-        <v>-0.0753957949215589</v>
+        <v>-0.0479741225942099</v>
       </c>
       <c r="I4" s="4">
-        <v>-7.539579492155895</v>
+        <v>-4.797412259420992</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -18586,16 +18586,16 @@
         <v>13.867</v>
       </c>
       <c r="F10" s="4">
-        <v>12.67684</v>
+        <v>13.50964</v>
       </c>
       <c r="G10" s="4">
-        <v>-1.190160000000001</v>
+        <v>-0.3573600000000017</v>
       </c>
       <c r="H10" s="4">
-        <v>-0.0858267830100238</v>
+        <v>-0.0257705343621548</v>
       </c>
       <c r="I10" s="4">
-        <v>-8.582678301002383</v>
+        <v>-2.577053436215488</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -18760,16 +18760,16 @@
         <v>1319.352</v>
       </c>
       <c r="F16" s="4">
-        <v>1220.718566</v>
+        <v>1253.521788</v>
       </c>
       <c r="G16" s="4">
-        <v>-98.63343400000008</v>
+        <v>-65.83021199999985</v>
       </c>
       <c r="H16" s="4">
-        <v>-0.07475899835676909</v>
+        <v>-0.0498958670620121</v>
       </c>
       <c r="I16" s="4">
-        <v>-7.475899835676914</v>
+        <v>-4.989586706201214</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -19005,28 +19005,28 @@
         <v>1488.984198645598</v>
       </c>
       <c r="E4" s="4">
-        <v>566.9802434772816</v>
+        <v>213.323633583905</v>
       </c>
       <c r="F4" s="4">
-        <v>421.6252505643341</v>
+        <v>132.8301467268623</v>
       </c>
       <c r="G4" s="4">
-        <v>38.07832507510927</v>
+        <v>14.32678961791182</v>
       </c>
       <c r="H4" s="4">
-        <v>28.31630120372336</v>
+        <v>8.920856705375826</v>
       </c>
       <c r="I4" s="4">
-        <v>-111.198006772009</v>
+        <v>-74.17405417607223</v>
       </c>
       <c r="J4" s="4">
-        <v>-7.468044783360117</v>
+        <v>-4.981520572450806</v>
       </c>
       <c r="K4" s="4">
-        <v>-7.468044783360117</v>
+        <v>-4.981520572450806</v>
       </c>
       <c r="L4" s="4">
-        <v>0.8437044474005821</v>
+        <v>0.9778747231770684</v>
       </c>
     </row>
     <row r="5" spans="1:12">
